--- a/Ecommerece_TestCases.xlsx
+++ b/Ecommerece_TestCases.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hulhubdrive-my.sharepoint.com/personal/saad1140_hulhub_com/Documents/Documents/New folder/SQA_Ecommerece_Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="11_F25DC773A252ABDACC10482991DF4F625BDE58EB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1E0934C5-0B42-4A15-B07B-B584E4A1DEDE}"/>
+  <xr:revisionPtr revIDLastSave="201" documentId="11_F25DC773A252ABDACC10482991DF4F625BDE58EB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A0E0D23A-F14F-4B8F-A18B-0C3AC1208359}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Login Module Test Cases" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="65">
   <si>
     <t>TC_ID</t>
   </si>
@@ -49,13 +49,212 @@
   </si>
   <si>
     <t>Actual Result</t>
+  </si>
+  <si>
+    <t>TC-001</t>
+  </si>
+  <si>
+    <t>TC-002</t>
+  </si>
+  <si>
+    <t>TC-003</t>
+  </si>
+  <si>
+    <t>TC-004</t>
+  </si>
+  <si>
+    <t>TC-005</t>
+  </si>
+  <si>
+    <t>TC-006</t>
+  </si>
+  <si>
+    <t>TC-007</t>
+  </si>
+  <si>
+    <t>TC-008</t>
+  </si>
+  <si>
+    <t>TC-009</t>
+  </si>
+  <si>
+    <t>TC-010</t>
+  </si>
+  <si>
+    <t>Login</t>
+  </si>
+  <si>
+    <t>Verify login with valid credentials</t>
+  </si>
+  <si>
+    <t>Verify login with empty email field</t>
+  </si>
+  <si>
+    <t>Verify login with empty password field</t>
+  </si>
+  <si>
+    <t>Verify password field masks entered characters</t>
+  </si>
+  <si>
+    <t>Verify login with invalid password</t>
+  </si>
+  <si>
+    <t>Verify login with invalid email</t>
+  </si>
+  <si>
+    <t>Verify forgotten password functionality</t>
+  </si>
+  <si>
+    <t>Verify Sucessful logout after login</t>
+  </si>
+  <si>
+    <t>Verify login after browser refresh</t>
+  </si>
+  <si>
+    <t>user account exists</t>
+  </si>
+  <si>
+    <t>none</t>
+  </si>
+  <si>
+    <t>login page is open</t>
+  </si>
+  <si>
+    <t>user logged in</t>
+  </si>
+  <si>
+    <t>user is logged in</t>
+  </si>
+  <si>
+    <t>1-Open login page
+2-Enter valid email
+3-Enter valid password
+4-Click Login</t>
+  </si>
+  <si>
+    <t>1-Open login page
+2-Enter valid email
+3-Enter invalid password
+4-Click Login</t>
+  </si>
+  <si>
+    <t>1-Open login page
+2-Enter invalid email
+3-Enter valid password
+4-Click Login</t>
+  </si>
+  <si>
+    <t>1-Open login page
+2-Leave  email blank
+3-Enter valid password
+4-Click Login</t>
+  </si>
+  <si>
+    <t>1-Open login page
+2-Enter valid email
+3-Leave password blank
+4-Click Login</t>
+  </si>
+  <si>
+    <t>1-Open login page
+2-Leave email blank
+3-Leave password blank
+4-Click Login</t>
+  </si>
+  <si>
+    <t>Click forgotten password</t>
+  </si>
+  <si>
+    <t>Click Logout from My Account</t>
+  </si>
+  <si>
+    <t>Login sucessfully, then refresh the browser</t>
+  </si>
+  <si>
+    <t>url:https://demo.opencart.com/en-gb?route=account/login</t>
+  </si>
+  <si>
+    <t>url:https://demo.opencart.com/en-gb?route=account/login
+Email: abc@test.com
+password: Wrong123</t>
+  </si>
+  <si>
+    <t>url:https://demo.opencart.com/en-gb?route=account/login
+Email: 
+password: Test@123</t>
+  </si>
+  <si>
+    <t>Verify login with both email and password empty field</t>
+  </si>
+  <si>
+    <t>Test@123</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>Valid credentials</t>
+  </si>
+  <si>
+    <t>User is sucessfully logged in and redirected to my account page</t>
+  </si>
+  <si>
+    <t>Error Message:  Warning: No match for E-Mail Address and/or Password.</t>
+  </si>
+  <si>
+    <t>Password is displayed as masked characters</t>
+  </si>
+  <si>
+    <t>User is redirected to the password reset page</t>
+  </si>
+  <si>
+    <t>User sucessfully logout and confirmation page is displayed</t>
+  </si>
+  <si>
+    <t>User remains logged in and Session is mantained</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>url:https://demo.opencart.com/en-gb?route=account/login
+Email: userabc@test.com
+password: Test@123</t>
+  </si>
+  <si>
+    <t>url:https://demo.opencart.com/en-gb?route=account/login
+Email: userabc@test.com
+password: Wrong123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">url:https://demo.opencart.com/en-gb?route=account/login
+Email: userabc@test.com
+password: </t>
+  </si>
+  <si>
+    <t>Pass</t>
+  </si>
+  <si>
+    <t>Type password in password field</t>
+  </si>
+  <si>
+    <t>Error Message:  Warning: Email field must be non empty</t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>Error Message:  Warning: Password field must be non empty</t>
+  </si>
+  <si>
+    <t>Error Message:  Warning: Email and password  field must be non empty</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -63,13 +262,39 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC00000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -84,8 +309,29 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -101,6 +347,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -366,41 +616,341 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.28515625" customWidth="1"/>
+    <col min="2" max="2" width="16.85546875" customWidth="1"/>
+    <col min="3" max="3" width="53.7109375" customWidth="1"/>
+    <col min="4" max="4" width="21.5703125" customWidth="1"/>
+    <col min="5" max="5" width="40" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="55.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="31.85546875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="29.5703125" customWidth="1"/>
+    <col min="9" max="9" width="13.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="I1" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F8" t="s">
+        <v>46</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>59</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Ecommerece_TestCases.xlsx
+++ b/Ecommerece_TestCases.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hulhubdrive-my.sharepoint.com/personal/saad1140_hulhub_com/Documents/Documents/New folder/SQA_Ecommerece_Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="201" documentId="11_F25DC773A252ABDACC10482991DF4F625BDE58EB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A0E0D23A-F14F-4B8F-A18B-0C3AC1208359}"/>
+  <xr:revisionPtr revIDLastSave="339" documentId="11_F25DC773A252ABDACC10482991DF4F625BDE58EB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{48F1ADD6-9EEF-4A5C-ACB5-3AD022BB8453}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Login Module Test Cases" sheetId="1" r:id="rId1"/>
+    <sheet name="Registration Module Test Cases" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="131">
   <si>
     <t>TC_ID</t>
   </si>
@@ -248,6 +249,204 @@
   </si>
   <si>
     <t>Error Message:  Warning: Email and password  field must be non empty</t>
+  </si>
+  <si>
+    <t>TC-011</t>
+  </si>
+  <si>
+    <t>TC-012</t>
+  </si>
+  <si>
+    <t>TC-013</t>
+  </si>
+  <si>
+    <t>TC-014</t>
+  </si>
+  <si>
+    <t>TC-015</t>
+  </si>
+  <si>
+    <t>TC-016</t>
+  </si>
+  <si>
+    <t>TC-017</t>
+  </si>
+  <si>
+    <t>TC-018</t>
+  </si>
+  <si>
+    <t>TC-019</t>
+  </si>
+  <si>
+    <t>TC-020</t>
+  </si>
+  <si>
+    <t>TC-021</t>
+  </si>
+  <si>
+    <t>TC-022</t>
+  </si>
+  <si>
+    <t>TC-023</t>
+  </si>
+  <si>
+    <t>TC-024</t>
+  </si>
+  <si>
+    <t>TC-025</t>
+  </si>
+  <si>
+    <t>Registration</t>
+  </si>
+  <si>
+    <t>Verify registration with valid details</t>
+  </si>
+  <si>
+    <t>Verify registration with an existing email address</t>
+  </si>
+  <si>
+    <t>Verify registration with all mandatory fields left blank</t>
+  </si>
+  <si>
+    <t>Verify registration with an invalid email format</t>
+  </si>
+  <si>
+    <t>Verify registration without accepting privacy policy</t>
+  </si>
+  <si>
+    <t>Verify registration with minimum valid password</t>
+  </si>
+  <si>
+    <t>Verify registraion with first name field empty</t>
+  </si>
+  <si>
+    <t>Verify registraion with last name field empty</t>
+  </si>
+  <si>
+    <t>Verify registraion with email field empty</t>
+  </si>
+  <si>
+    <t>Verify registration with password field empty</t>
+  </si>
+  <si>
+    <t>Verify registration without subscribing news letter</t>
+  </si>
+  <si>
+    <t>Verify sucessful registration redirects user to account success page</t>
+  </si>
+  <si>
+    <t>Verify registration with less than minimum password allowed length</t>
+  </si>
+  <si>
+    <t>Verify registration exceeding with maxmium password allowed length</t>
+  </si>
+  <si>
+    <t>User is on registration page</t>
+  </si>
+  <si>
+    <t>Existing account is available</t>
+  </si>
+  <si>
+    <t>Registration page is open</t>
+  </si>
+  <si>
+    <t>user complete registration sucessfully</t>
+  </si>
+  <si>
+    <t>Fill all mandatory fields and click continue</t>
+  </si>
+  <si>
+    <t>Enter already registered user email</t>
+  </si>
+  <si>
+    <t>Click continue without entering any data</t>
+  </si>
+  <si>
+    <t>Enter invalid email and submit</t>
+  </si>
+  <si>
+    <t>Fill data but don't check privacy and policy</t>
+  </si>
+  <si>
+    <t>Enter password with minimum allowed values</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fill all fields except firt name and than submit </t>
+  </si>
+  <si>
+    <t>Fill all fields except password field and than submit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fill all fields except last name and than submit </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fill all fields except email and than submit </t>
+  </si>
+  <si>
+    <t>Submit valid registration form</t>
+  </si>
+  <si>
+    <t>Verify registration subscribing news letter</t>
+  </si>
+  <si>
+    <t>Select yes for news letter and register</t>
+  </si>
+  <si>
+    <t>Select no for news letter and register</t>
+  </si>
+  <si>
+    <t>Fill password field exceeding maximum length</t>
+  </si>
+  <si>
+    <t>New user details</t>
+  </si>
+  <si>
+    <t>Existing email</t>
+  </si>
+  <si>
+    <t>abc.com</t>
+  </si>
+  <si>
+    <t>valid details</t>
+  </si>
+  <si>
+    <t>Fill password field  less than minimum length</t>
+  </si>
+  <si>
+    <t>Invalid password length</t>
+  </si>
+  <si>
+    <t>Account is created sucessfully and success page is displayed</t>
+  </si>
+  <si>
+    <t>Warning message email is already registered</t>
+  </si>
+  <si>
+    <t>Validation message are displayed for all mandatory fields</t>
+  </si>
+  <si>
+    <t>User should not be registered and email validation message should appear</t>
+  </si>
+  <si>
+    <t>User should not be registered and  warning message appear to accept privacy and policy</t>
+  </si>
+  <si>
+    <t>User should follow the application password rule</t>
+  </si>
+  <si>
+    <t>Validation message for the first name is displayed</t>
+  </si>
+  <si>
+    <t>Validation message for the last name is displayed</t>
+  </si>
+  <si>
+    <t>Validation message for the email is displayed</t>
+  </si>
+  <si>
+    <t>User is redirected to your account has been created page</t>
+  </si>
+  <si>
+    <t>Validation for password filed message should be displayed</t>
   </si>
 </sst>
 </file>
@@ -953,4 +1152,399 @@
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FED5E2F0-4F96-4FAB-AF17-AFD3C1B875BE}">
+  <dimension ref="A1:I16"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.5703125" customWidth="1"/>
+    <col min="2" max="2" width="14.5703125" customWidth="1"/>
+    <col min="3" max="3" width="34.85546875" customWidth="1"/>
+    <col min="4" max="4" width="22.7109375" customWidth="1"/>
+    <col min="5" max="5" width="28.140625" customWidth="1"/>
+    <col min="6" max="6" width="18.85546875" customWidth="1"/>
+    <col min="7" max="7" width="22.42578125" customWidth="1"/>
+    <col min="8" max="8" width="20.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>69</v>
+      </c>
+      <c r="B6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>70</v>
+      </c>
+      <c r="B7" t="s">
+        <v>80</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>71</v>
+      </c>
+      <c r="B8" t="s">
+        <v>80</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>72</v>
+      </c>
+      <c r="B9" t="s">
+        <v>80</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>73</v>
+      </c>
+      <c r="B10" t="s">
+        <v>80</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>74</v>
+      </c>
+      <c r="B11" t="s">
+        <v>80</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>75</v>
+      </c>
+      <c r="B12" t="s">
+        <v>80</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>76</v>
+      </c>
+      <c r="B13" t="s">
+        <v>80</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>77</v>
+      </c>
+      <c r="B14" t="s">
+        <v>80</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>78</v>
+      </c>
+      <c r="B15" t="s">
+        <v>80</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>79</v>
+      </c>
+      <c r="B16" t="s">
+        <v>80</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>